--- a/backend/scripts/audit-output/expeditor-smoke/ex-5.2.0.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-5.2.0.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
-  <si>
-    <t>Загрузочный лист 5.2.0 (Время печати: 27.05.2026 19:51:41)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t>Загрузочный лист 5.2.0 (Время печати: 28.05.2026 17:37:20)</t>
   </si>
   <si>
     <t>Дата заказа:</t>
@@ -561,7 +561,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
